--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117660016</v>
+        <v>117659625</v>
       </c>
       <c r="B6" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,27 +1206,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         <v>763017</v>
       </c>
       <c r="R6" t="n">
-        <v>7308299</v>
+        <v>7308302</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117659625</v>
+        <v>117664460</v>
       </c>
       <c r="B7" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,34 +1312,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1347,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763017</v>
+        <v>762971</v>
       </c>
       <c r="R7" t="n">
-        <v>7308302</v>
+        <v>7308322</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1385,13 +1382,17 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,17 +1404,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117664460</v>
+        <v>117660016</v>
       </c>
       <c r="B8" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,31 +1423,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1454,10 +1458,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762971</v>
+        <v>763017</v>
       </c>
       <c r="R8" t="n">
-        <v>7308322</v>
+        <v>7308299</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1492,17 +1496,13 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117659625</v>
+        <v>117660016</v>
       </c>
       <c r="B6" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,27 +1206,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         <v>763017</v>
       </c>
       <c r="R6" t="n">
-        <v>7308302</v>
+        <v>7308299</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1303,7 +1303,7 @@
         <v>117664460</v>
       </c>
       <c r="B7" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117660016</v>
+        <v>117659625</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,27 +1427,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1461,7 +1461,7 @@
         <v>763017</v>
       </c>
       <c r="R8" t="n">
-        <v>7308299</v>
+        <v>7308302</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119633173</v>
+        <v>119693821</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>91310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763074</v>
+        <v>762948</v>
       </c>
       <c r="R9" t="n">
-        <v>7308093</v>
+        <v>7308159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633182</v>
+        <v>119633199</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762980</v>
+        <v>763016</v>
       </c>
       <c r="R10" t="n">
-        <v>7308167</v>
+        <v>7308037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119693821</v>
+        <v>119633173</v>
       </c>
       <c r="B11" t="n">
-        <v>91310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1958</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762948</v>
+        <v>763074</v>
       </c>
       <c r="R11" t="n">
-        <v>7308159</v>
+        <v>7308093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633199</v>
+        <v>119633182</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763016</v>
+        <v>762980</v>
       </c>
       <c r="R12" t="n">
-        <v>7308037</v>
+        <v>7308167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633141</v>
+        <v>119633156</v>
       </c>
       <c r="B24" t="n">
-        <v>87406</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762975</v>
+        <v>763021</v>
       </c>
       <c r="R24" t="n">
-        <v>7308144</v>
+        <v>7308073</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633190</v>
+        <v>119633141</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3165,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>762983</v>
+        <v>762975</v>
       </c>
       <c r="R25" t="n">
-        <v>7308145</v>
+        <v>7308144</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633197</v>
+        <v>119633190</v>
       </c>
       <c r="B26" t="n">
         <v>91840</v>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763052</v>
+        <v>762983</v>
       </c>
       <c r="R26" t="n">
-        <v>7308043</v>
+        <v>7308145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633191</v>
+        <v>119633197</v>
       </c>
       <c r="B27" t="n">
         <v>91840</v>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762980</v>
+        <v>763052</v>
       </c>
       <c r="R27" t="n">
-        <v>7308100</v>
+        <v>7308043</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119633156</v>
+        <v>119633191</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>763021</v>
+        <v>762980</v>
       </c>
       <c r="R28" t="n">
-        <v>7308073</v>
+        <v>7308100</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633195</v>
+        <v>119633168</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>97941</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>763021</v>
+        <v>763065</v>
       </c>
       <c r="R29" t="n">
-        <v>7308061</v>
+        <v>7308164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633201</v>
+        <v>119633195</v>
       </c>
       <c r="B30" t="n">
         <v>91840</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763056</v>
+        <v>763021</v>
       </c>
       <c r="R30" t="n">
-        <v>7308031</v>
+        <v>7308061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633206</v>
+        <v>119633201</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,25 +3777,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>763047</v>
+        <v>763056</v>
       </c>
       <c r="R31" t="n">
-        <v>7308006</v>
+        <v>7308031</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119633189</v>
+        <v>119633206</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,25 +3879,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>762957</v>
+        <v>763047</v>
       </c>
       <c r="R32" t="n">
-        <v>7308152</v>
+        <v>7308006</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633168</v>
+        <v>119633189</v>
       </c>
       <c r="B33" t="n">
-        <v>97941</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763065</v>
+        <v>762957</v>
       </c>
       <c r="R33" t="n">
-        <v>7308164</v>
+        <v>7308152</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633148</v>
+        <v>119633169</v>
       </c>
       <c r="B49" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762994</v>
+        <v>762961</v>
       </c>
       <c r="R49" t="n">
-        <v>7308094</v>
+        <v>7308137</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633169</v>
+        <v>119633147</v>
       </c>
       <c r="B50" t="n">
-        <v>78263</v>
+        <v>91463</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762961</v>
+        <v>762967</v>
       </c>
       <c r="R50" t="n">
-        <v>7308137</v>
+        <v>7308150</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119633147</v>
+        <v>119633148</v>
       </c>
       <c r="B51" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762967</v>
+        <v>762994</v>
       </c>
       <c r="R51" t="n">
-        <v>7308150</v>
+        <v>7308094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -3561,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633168</v>
+        <v>119633195</v>
       </c>
       <c r="B29" t="n">
-        <v>97941</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>763065</v>
+        <v>763021</v>
       </c>
       <c r="R29" t="n">
-        <v>7308164</v>
+        <v>7308061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633195</v>
+        <v>119633201</v>
       </c>
       <c r="B30" t="n">
         <v>91840</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763021</v>
+        <v>763056</v>
       </c>
       <c r="R30" t="n">
-        <v>7308061</v>
+        <v>7308031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633201</v>
+        <v>119633206</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,25 +3777,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>763056</v>
+        <v>763047</v>
       </c>
       <c r="R31" t="n">
-        <v>7308031</v>
+        <v>7308006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119633206</v>
+        <v>119633189</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,25 +3879,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>763047</v>
+        <v>762957</v>
       </c>
       <c r="R32" t="n">
-        <v>7308006</v>
+        <v>7308152</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633189</v>
+        <v>119633168</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>97941</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>762957</v>
+        <v>763065</v>
       </c>
       <c r="R33" t="n">
-        <v>7308152</v>
+        <v>7308164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119693821</v>
+        <v>119633148</v>
       </c>
       <c r="B9" t="n">
-        <v>91310</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1958</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762948</v>
+        <v>762994</v>
       </c>
       <c r="R9" t="n">
-        <v>7308159</v>
+        <v>7308094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633199</v>
+        <v>119633179</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763016</v>
+        <v>763037</v>
       </c>
       <c r="R10" t="n">
-        <v>7308037</v>
+        <v>7308211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633173</v>
+        <v>119633175</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763074</v>
+        <v>763065</v>
       </c>
       <c r="R11" t="n">
-        <v>7308093</v>
+        <v>7308131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633182</v>
+        <v>119633153</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762980</v>
+        <v>763033</v>
       </c>
       <c r="R12" t="n">
-        <v>7308167</v>
+        <v>7308027</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633192</v>
+        <v>119633164</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,25 +1941,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762993</v>
+        <v>762989</v>
       </c>
       <c r="R13" t="n">
-        <v>7308094</v>
+        <v>7308098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633178</v>
+        <v>119633145</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763088</v>
+        <v>763013</v>
       </c>
       <c r="R14" t="n">
-        <v>7308206</v>
+        <v>7308032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633205</v>
+        <v>119633173</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,25 +2145,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763062</v>
+        <v>763074</v>
       </c>
       <c r="R15" t="n">
-        <v>7308017</v>
+        <v>7308093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633140</v>
+        <v>119633206</v>
       </c>
       <c r="B16" t="n">
-        <v>87406</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763083</v>
+        <v>763047</v>
       </c>
       <c r="R16" t="n">
-        <v>7308099</v>
+        <v>7308006</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633155</v>
+        <v>119633172</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763047</v>
+        <v>763017</v>
       </c>
       <c r="R17" t="n">
-        <v>7308003</v>
+        <v>7308064</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633175</v>
+        <v>119633177</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763065</v>
+        <v>763084</v>
       </c>
       <c r="R18" t="n">
-        <v>7308131</v>
+        <v>7308169</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633200</v>
+        <v>119633205</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763027</v>
+        <v>763062</v>
       </c>
       <c r="R19" t="n">
-        <v>7308025</v>
+        <v>7308017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119633179</v>
+        <v>119633183</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>89252</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>763037</v>
+        <v>763073</v>
       </c>
       <c r="R20" t="n">
-        <v>7308211</v>
+        <v>7307993</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119633160</v>
+        <v>119633161</v>
       </c>
       <c r="B21" t="n">
         <v>91856</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>763056</v>
+        <v>763036</v>
       </c>
       <c r="R21" t="n">
-        <v>7308022</v>
+        <v>7308015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633202</v>
+        <v>119633160</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,25 +2859,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>763053</v>
+        <v>763056</v>
       </c>
       <c r="R22" t="n">
-        <v>7307990</v>
+        <v>7308022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119633207</v>
+        <v>119633194</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,25 +2961,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>763047</v>
+        <v>763027</v>
       </c>
       <c r="R23" t="n">
-        <v>7308005</v>
+        <v>7308069</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633156</v>
+        <v>119633192</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,25 +3063,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>763021</v>
+        <v>762993</v>
       </c>
       <c r="R24" t="n">
-        <v>7308073</v>
+        <v>7308094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633141</v>
+        <v>119633168</v>
       </c>
       <c r="B25" t="n">
-        <v>87406</v>
+        <v>97941</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3165,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>762975</v>
+        <v>763065</v>
       </c>
       <c r="R25" t="n">
-        <v>7308144</v>
+        <v>7308164</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633190</v>
+        <v>119633178</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>762983</v>
+        <v>763088</v>
       </c>
       <c r="R26" t="n">
-        <v>7308145</v>
+        <v>7308206</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633197</v>
+        <v>119633198</v>
       </c>
       <c r="B27" t="n">
         <v>91840</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763052</v>
+        <v>763018</v>
       </c>
       <c r="R27" t="n">
         <v>7308043</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633195</v>
+        <v>119633169</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3573,25 +3573,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>763021</v>
+        <v>762961</v>
       </c>
       <c r="R29" t="n">
-        <v>7308061</v>
+        <v>7308137</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633201</v>
+        <v>119633166</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,25 +3675,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763056</v>
+        <v>763003</v>
       </c>
       <c r="R30" t="n">
-        <v>7308031</v>
+        <v>7308087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633206</v>
+        <v>119633181</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,25 +3777,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>763047</v>
+        <v>762986</v>
       </c>
       <c r="R31" t="n">
-        <v>7308006</v>
+        <v>7308167</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119633189</v>
+        <v>119633202</v>
       </c>
       <c r="B32" t="n">
         <v>91840</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>762957</v>
+        <v>763053</v>
       </c>
       <c r="R32" t="n">
-        <v>7308152</v>
+        <v>7307990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633168</v>
+        <v>119633195</v>
       </c>
       <c r="B33" t="n">
-        <v>97941</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763065</v>
+        <v>763021</v>
       </c>
       <c r="R33" t="n">
-        <v>7308164</v>
+        <v>7308061</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119633176</v>
+        <v>119633182</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>763069</v>
+        <v>762980</v>
       </c>
       <c r="R34" t="n">
-        <v>7308161</v>
+        <v>7308167</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119633164</v>
+        <v>119633156</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762989</v>
+        <v>763021</v>
       </c>
       <c r="R35" t="n">
-        <v>7308098</v>
+        <v>7308073</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119633196</v>
+        <v>119633176</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>763027</v>
+        <v>763069</v>
       </c>
       <c r="R36" t="n">
-        <v>7308050</v>
+        <v>7308161</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119633177</v>
+        <v>119633147</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4389,25 +4389,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>763084</v>
+        <v>762967</v>
       </c>
       <c r="R37" t="n">
-        <v>7308169</v>
+        <v>7308150</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119633203</v>
+        <v>119633157</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>57326</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762970</v>
+        <v>763063</v>
       </c>
       <c r="R38" t="n">
-        <v>7308156</v>
+        <v>7308218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119633167</v>
+        <v>119693821</v>
       </c>
       <c r="B39" t="n">
-        <v>91832</v>
+        <v>91310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4593,25 +4593,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>763047</v>
+        <v>762948</v>
       </c>
       <c r="R39" t="n">
-        <v>7308008</v>
+        <v>7308159</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119633145</v>
+        <v>119633143</v>
       </c>
       <c r="B40" t="n">
-        <v>91826</v>
+        <v>89275</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4695,25 +4695,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>763013</v>
+        <v>762995</v>
       </c>
       <c r="R40" t="n">
-        <v>7308032</v>
+        <v>7308094</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4759,6 +4759,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4785,10 +4790,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119633170</v>
+        <v>119633142</v>
       </c>
       <c r="B41" t="n">
-        <v>93935</v>
+        <v>89275</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4797,25 +4802,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2387</v>
+        <v>6286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>763074</v>
+        <v>762980</v>
       </c>
       <c r="R41" t="n">
-        <v>7308155</v>
+        <v>7308130</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4887,10 +4892,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119633194</v>
+        <v>119633174</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4899,25 +4904,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4927,10 +4932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>763027</v>
+        <v>763074</v>
       </c>
       <c r="R42" t="n">
-        <v>7308069</v>
+        <v>7308105</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,10 +4994,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119633183</v>
+        <v>119633196</v>
       </c>
       <c r="B43" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5001,25 +5006,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>763073</v>
+        <v>763027</v>
       </c>
       <c r="R43" t="n">
-        <v>7307993</v>
+        <v>7308050</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,10 +5096,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633174</v>
+        <v>119633159</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5103,25 +5108,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5131,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763074</v>
+        <v>763019</v>
       </c>
       <c r="R44" t="n">
-        <v>7308105</v>
+        <v>7308034</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633204</v>
+        <v>119633155</v>
       </c>
       <c r="B45" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5209,21 +5214,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763023</v>
+        <v>763047</v>
       </c>
       <c r="R45" t="n">
-        <v>7308047</v>
+        <v>7308003</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,10 +5300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633163</v>
+        <v>119633149</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5311,21 +5316,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5335,10 +5340,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762953</v>
+        <v>763032</v>
       </c>
       <c r="R46" t="n">
-        <v>7308131</v>
+        <v>7308054</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5397,7 +5402,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633198</v>
+        <v>119633201</v>
       </c>
       <c r="B47" t="n">
         <v>91840</v>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>763018</v>
+        <v>763056</v>
       </c>
       <c r="R47" t="n">
-        <v>7308043</v>
+        <v>7308031</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5499,10 +5504,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119633162</v>
+        <v>119633199</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5511,25 +5516,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5539,10 +5544,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>763091</v>
+        <v>763016</v>
       </c>
       <c r="R48" t="n">
-        <v>7308033</v>
+        <v>7308037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5601,10 +5606,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633169</v>
+        <v>119633163</v>
       </c>
       <c r="B49" t="n">
-        <v>78263</v>
+        <v>91832</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5617,21 +5622,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5641,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762961</v>
+        <v>762953</v>
       </c>
       <c r="R49" t="n">
-        <v>7308137</v>
+        <v>7308131</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5703,10 +5708,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633147</v>
+        <v>119633141</v>
       </c>
       <c r="B50" t="n">
-        <v>91463</v>
+        <v>87406</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5719,21 +5724,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4745</v>
+        <v>4412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5743,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762967</v>
+        <v>762975</v>
       </c>
       <c r="R50" t="n">
-        <v>7308150</v>
+        <v>7308144</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5805,10 +5810,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119633148</v>
+        <v>119633167</v>
       </c>
       <c r="B51" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5821,21 +5826,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762994</v>
+        <v>763047</v>
       </c>
       <c r="R51" t="n">
-        <v>7308094</v>
+        <v>7308008</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5907,10 +5912,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119633159</v>
+        <v>119633190</v>
       </c>
       <c r="B52" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5919,25 +5924,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5947,10 +5952,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>763019</v>
+        <v>762983</v>
       </c>
       <c r="R52" t="n">
-        <v>7308034</v>
+        <v>7308145</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6009,10 +6014,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119633172</v>
+        <v>119633197</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6021,25 +6026,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6049,10 +6054,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>763017</v>
+        <v>763052</v>
       </c>
       <c r="R53" t="n">
-        <v>7308064</v>
+        <v>7308043</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6111,10 +6116,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119633150</v>
+        <v>119633207</v>
       </c>
       <c r="B54" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6127,21 +6132,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6151,10 +6156,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>763017</v>
+        <v>763047</v>
       </c>
       <c r="R54" t="n">
-        <v>7308038</v>
+        <v>7308005</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6213,10 +6218,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119633143</v>
+        <v>119633204</v>
       </c>
       <c r="B55" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6225,25 +6230,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>762995</v>
+        <v>763023</v>
       </c>
       <c r="R55" t="n">
-        <v>7308094</v>
+        <v>7308047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6289,11 +6294,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6320,10 +6320,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119633153</v>
+        <v>119633200</v>
       </c>
       <c r="B56" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6332,25 +6332,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>763033</v>
+        <v>763027</v>
       </c>
       <c r="R56" t="n">
-        <v>7308027</v>
+        <v>7308025</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119633166</v>
+        <v>119633162</v>
       </c>
       <c r="B57" t="n">
         <v>91832</v>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>763003</v>
+        <v>763091</v>
       </c>
       <c r="R57" t="n">
-        <v>7308087</v>
+        <v>7308033</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119633161</v>
+        <v>119633150</v>
       </c>
       <c r="B58" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763036</v>
+        <v>763017</v>
       </c>
       <c r="R58" t="n">
-        <v>7308015</v>
+        <v>7308038</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633149</v>
+        <v>119633203</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6744,21 +6744,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>763032</v>
+        <v>762970</v>
       </c>
       <c r="R60" t="n">
-        <v>7308054</v>
+        <v>7308156</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633157</v>
+        <v>119633140</v>
       </c>
       <c r="B61" t="n">
-        <v>57326</v>
+        <v>87406</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>763063</v>
+        <v>763083</v>
       </c>
       <c r="R61" t="n">
-        <v>7308218</v>
+        <v>7308099</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119633181</v>
+        <v>119633170</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>93935</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6944,25 +6944,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>762986</v>
+        <v>763074</v>
       </c>
       <c r="R62" t="n">
-        <v>7308167</v>
+        <v>7308155</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119633142</v>
+        <v>119633189</v>
       </c>
       <c r="B63" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>762980</v>
+        <v>762957</v>
       </c>
       <c r="R63" t="n">
-        <v>7308130</v>
+        <v>7308152</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119633176</v>
+        <v>119633157</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4287,25 +4287,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>763069</v>
+        <v>763063</v>
       </c>
       <c r="R36" t="n">
-        <v>7308161</v>
+        <v>7308218</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119633157</v>
+        <v>119633176</v>
       </c>
       <c r="B38" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,25 +4491,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>763063</v>
+        <v>763069</v>
       </c>
       <c r="R38" t="n">
-        <v>7308218</v>
+        <v>7308161</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633203</v>
+        <v>119633189</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6740,25 +6740,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762970</v>
+        <v>762957</v>
       </c>
       <c r="R60" t="n">
-        <v>7308156</v>
+        <v>7308152</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633140</v>
+        <v>119633203</v>
       </c>
       <c r="B61" t="n">
-        <v>87406</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>763083</v>
+        <v>762970</v>
       </c>
       <c r="R61" t="n">
-        <v>7308099</v>
+        <v>7308156</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119633170</v>
+        <v>119633140</v>
       </c>
       <c r="B62" t="n">
-        <v>93935</v>
+        <v>87406</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6944,25 +6944,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2387</v>
+        <v>4412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>763074</v>
+        <v>763083</v>
       </c>
       <c r="R62" t="n">
-        <v>7308155</v>
+        <v>7308099</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119633189</v>
+        <v>119633170</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>93935</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2387</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>762957</v>
+        <v>763074</v>
       </c>
       <c r="R63" t="n">
-        <v>7308152</v>
+        <v>7308155</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119633148</v>
+        <v>119633140</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>87406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762994</v>
+        <v>763083</v>
       </c>
       <c r="R9" t="n">
-        <v>7308094</v>
+        <v>7308099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633179</v>
+        <v>119633189</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763037</v>
+        <v>762957</v>
       </c>
       <c r="R10" t="n">
-        <v>7308211</v>
+        <v>7308152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633175</v>
+        <v>119633162</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,25 +1737,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763065</v>
+        <v>763091</v>
       </c>
       <c r="R11" t="n">
-        <v>7308131</v>
+        <v>7308033</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633153</v>
+        <v>119633179</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763033</v>
+        <v>763037</v>
       </c>
       <c r="R12" t="n">
-        <v>7308027</v>
+        <v>7308211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633164</v>
+        <v>119633205</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762989</v>
+        <v>763062</v>
       </c>
       <c r="R13" t="n">
-        <v>7308098</v>
+        <v>7308017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633145</v>
+        <v>119633190</v>
       </c>
       <c r="B14" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763013</v>
+        <v>762983</v>
       </c>
       <c r="R14" t="n">
-        <v>7308032</v>
+        <v>7308145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633173</v>
+        <v>119633182</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763074</v>
+        <v>762980</v>
       </c>
       <c r="R15" t="n">
-        <v>7308093</v>
+        <v>7308167</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633206</v>
+        <v>119633173</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763047</v>
+        <v>763074</v>
       </c>
       <c r="R16" t="n">
-        <v>7308006</v>
+        <v>7308093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633172</v>
+        <v>119633207</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763017</v>
+        <v>763047</v>
       </c>
       <c r="R17" t="n">
-        <v>7308064</v>
+        <v>7308005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,10 +2439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633177</v>
+        <v>119633195</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,25 +2451,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763084</v>
+        <v>763021</v>
       </c>
       <c r="R18" t="n">
-        <v>7308169</v>
+        <v>7308061</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633205</v>
+        <v>119633197</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763062</v>
+        <v>763052</v>
       </c>
       <c r="R19" t="n">
-        <v>7308017</v>
+        <v>7308043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119633183</v>
+        <v>119633202</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>763073</v>
+        <v>763053</v>
       </c>
       <c r="R20" t="n">
-        <v>7307993</v>
+        <v>7307990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119633161</v>
+        <v>119633167</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>763036</v>
+        <v>763047</v>
       </c>
       <c r="R21" t="n">
-        <v>7308015</v>
+        <v>7308008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633160</v>
+        <v>119633201</v>
       </c>
       <c r="B22" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,25 +2859,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
         <v>763056</v>
       </c>
       <c r="R22" t="n">
-        <v>7308022</v>
+        <v>7308031</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119633194</v>
+        <v>119633163</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,25 +2961,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>763027</v>
+        <v>762953</v>
       </c>
       <c r="R23" t="n">
-        <v>7308069</v>
+        <v>7308131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633192</v>
+        <v>119633155</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,25 +3063,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762993</v>
+        <v>763047</v>
       </c>
       <c r="R24" t="n">
-        <v>7308094</v>
+        <v>7308003</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633168</v>
+        <v>119633156</v>
       </c>
       <c r="B25" t="n">
-        <v>97941</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3165,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>763065</v>
+        <v>763021</v>
       </c>
       <c r="R25" t="n">
-        <v>7308164</v>
+        <v>7308073</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633178</v>
+        <v>119633199</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763088</v>
+        <v>763016</v>
       </c>
       <c r="R26" t="n">
-        <v>7308206</v>
+        <v>7308037</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633198</v>
+        <v>119633170</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>93935</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2387</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763018</v>
+        <v>763074</v>
       </c>
       <c r="R27" t="n">
-        <v>7308043</v>
+        <v>7308155</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119633191</v>
+        <v>119633145</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>762980</v>
+        <v>763013</v>
       </c>
       <c r="R28" t="n">
-        <v>7308100</v>
+        <v>7308032</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633169</v>
+        <v>119633206</v>
       </c>
       <c r="B29" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762961</v>
+        <v>763047</v>
       </c>
       <c r="R29" t="n">
-        <v>7308137</v>
+        <v>7308006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633166</v>
+        <v>119633198</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,25 +3675,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763003</v>
+        <v>763018</v>
       </c>
       <c r="R30" t="n">
-        <v>7308087</v>
+        <v>7308043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633181</v>
+        <v>119633183</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>89252</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6276</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>762986</v>
+        <v>763073</v>
       </c>
       <c r="R31" t="n">
-        <v>7308167</v>
+        <v>7307993</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119633202</v>
+        <v>119633172</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,25 +3879,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>763053</v>
+        <v>763017</v>
       </c>
       <c r="R32" t="n">
-        <v>7307990</v>
+        <v>7308064</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633195</v>
+        <v>119633169</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763021</v>
+        <v>762961</v>
       </c>
       <c r="R33" t="n">
-        <v>7308061</v>
+        <v>7308137</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119633182</v>
+        <v>119633176</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>762980</v>
+        <v>763069</v>
       </c>
       <c r="R34" t="n">
-        <v>7308167</v>
+        <v>7308161</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119633156</v>
+        <v>119633181</v>
       </c>
       <c r="B35" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>763021</v>
+        <v>762986</v>
       </c>
       <c r="R35" t="n">
-        <v>7308073</v>
+        <v>7308167</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119633157</v>
+        <v>119633161</v>
       </c>
       <c r="B36" t="n">
-        <v>57326</v>
+        <v>91856</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>763063</v>
+        <v>763036</v>
       </c>
       <c r="R36" t="n">
-        <v>7308218</v>
+        <v>7308015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119633147</v>
+        <v>119633166</v>
       </c>
       <c r="B37" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>762967</v>
+        <v>763003</v>
       </c>
       <c r="R37" t="n">
-        <v>7308150</v>
+        <v>7308087</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119633176</v>
+        <v>119633141</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,25 +4491,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>763069</v>
+        <v>762975</v>
       </c>
       <c r="R38" t="n">
-        <v>7308161</v>
+        <v>7308144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119693821</v>
+        <v>119633150</v>
       </c>
       <c r="B39" t="n">
-        <v>91310</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4593,25 +4593,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1958</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>762948</v>
+        <v>763017</v>
       </c>
       <c r="R39" t="n">
-        <v>7308159</v>
+        <v>7308038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119633143</v>
+        <v>119633174</v>
       </c>
       <c r="B40" t="n">
-        <v>89275</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>762995</v>
+        <v>763074</v>
       </c>
       <c r="R40" t="n">
-        <v>7308094</v>
+        <v>7308105</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4759,11 +4759,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4790,10 +4785,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119633142</v>
+        <v>119633149</v>
       </c>
       <c r="B41" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4802,25 +4797,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4830,10 +4825,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>762980</v>
+        <v>763032</v>
       </c>
       <c r="R41" t="n">
-        <v>7308130</v>
+        <v>7308054</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,10 +4887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119633174</v>
+        <v>119633148</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4904,25 +4899,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4932,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>763074</v>
+        <v>762994</v>
       </c>
       <c r="R42" t="n">
-        <v>7308105</v>
+        <v>7308094</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,7 +4989,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119633196</v>
+        <v>119633192</v>
       </c>
       <c r="B43" t="n">
         <v>91840</v>
@@ -5034,10 +5029,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>763027</v>
+        <v>762993</v>
       </c>
       <c r="R43" t="n">
-        <v>7308050</v>
+        <v>7308094</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633159</v>
+        <v>119633168</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
+        <v>97941</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5108,25 +5103,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763019</v>
+        <v>763065</v>
       </c>
       <c r="R44" t="n">
-        <v>7308034</v>
+        <v>7308164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,10 +5193,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633155</v>
+        <v>119633159</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5214,21 +5209,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763047</v>
+        <v>763019</v>
       </c>
       <c r="R45" t="n">
-        <v>7308003</v>
+        <v>7308034</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,10 +5295,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633149</v>
+        <v>119633204</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5316,21 +5311,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5340,10 +5335,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>763032</v>
+        <v>763023</v>
       </c>
       <c r="R46" t="n">
-        <v>7308054</v>
+        <v>7308047</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,10 +5397,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633201</v>
+        <v>119633143</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5414,25 +5409,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>763056</v>
+        <v>762995</v>
       </c>
       <c r="R47" t="n">
-        <v>7308031</v>
+        <v>7308094</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5478,6 +5473,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,10 +5504,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119633199</v>
+        <v>119633157</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5516,25 +5516,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>763016</v>
+        <v>763063</v>
       </c>
       <c r="R48" t="n">
-        <v>7308037</v>
+        <v>7308218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633163</v>
+        <v>119633164</v>
       </c>
       <c r="B49" t="n">
         <v>91832</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762953</v>
+        <v>762989</v>
       </c>
       <c r="R49" t="n">
-        <v>7308131</v>
+        <v>7308098</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5708,10 +5708,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633141</v>
+        <v>119633200</v>
       </c>
       <c r="B50" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5720,25 +5720,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762975</v>
+        <v>763027</v>
       </c>
       <c r="R50" t="n">
-        <v>7308144</v>
+        <v>7308025</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5810,10 +5810,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119633167</v>
+        <v>119633191</v>
       </c>
       <c r="B51" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5822,25 +5822,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>763047</v>
+        <v>762980</v>
       </c>
       <c r="R51" t="n">
-        <v>7308008</v>
+        <v>7308100</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119633190</v>
+        <v>119633142</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5924,25 +5924,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762983</v>
+        <v>762980</v>
       </c>
       <c r="R52" t="n">
-        <v>7308145</v>
+        <v>7308130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6014,10 +6014,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119633197</v>
+        <v>119633153</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6026,25 +6026,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>763052</v>
+        <v>763033</v>
       </c>
       <c r="R53" t="n">
-        <v>7308043</v>
+        <v>7308027</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119633207</v>
+        <v>119633152</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>763047</v>
+        <v>763018</v>
       </c>
       <c r="R54" t="n">
-        <v>7308005</v>
+        <v>7308029</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119633204</v>
+        <v>119693821</v>
       </c>
       <c r="B55" t="n">
-        <v>91834</v>
+        <v>91310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>763023</v>
+        <v>762948</v>
       </c>
       <c r="R55" t="n">
-        <v>7308047</v>
+        <v>7308159</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119633200</v>
+        <v>119633194</v>
       </c>
       <c r="B56" t="n">
         <v>91840</v>
@@ -6363,7 +6363,7 @@
         <v>763027</v>
       </c>
       <c r="R56" t="n">
-        <v>7308025</v>
+        <v>7308069</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119633162</v>
+        <v>119633203</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>763091</v>
+        <v>762970</v>
       </c>
       <c r="R57" t="n">
-        <v>7308033</v>
+        <v>7308156</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119633150</v>
+        <v>119633160</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763017</v>
+        <v>763056</v>
       </c>
       <c r="R58" t="n">
-        <v>7308038</v>
+        <v>7308022</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119633152</v>
+        <v>119633196</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6638,25 +6638,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>763018</v>
+        <v>763027</v>
       </c>
       <c r="R59" t="n">
-        <v>7308029</v>
+        <v>7308050</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633189</v>
+        <v>119633147</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6740,25 +6740,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762957</v>
+        <v>762967</v>
       </c>
       <c r="R60" t="n">
-        <v>7308152</v>
+        <v>7308150</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633203</v>
+        <v>119633177</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6842,25 +6842,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>762970</v>
+        <v>763084</v>
       </c>
       <c r="R61" t="n">
-        <v>7308156</v>
+        <v>7308169</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119633140</v>
+        <v>119633178</v>
       </c>
       <c r="B62" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6944,25 +6944,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>763083</v>
+        <v>763088</v>
       </c>
       <c r="R62" t="n">
-        <v>7308099</v>
+        <v>7308206</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119633170</v>
+        <v>119633175</v>
       </c>
       <c r="B63" t="n">
-        <v>93935</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>763074</v>
+        <v>763065</v>
       </c>
       <c r="R63" t="n">
-        <v>7308155</v>
+        <v>7308131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633173</v>
+        <v>119633207</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763074</v>
+        <v>763047</v>
       </c>
       <c r="R16" t="n">
-        <v>7308093</v>
+        <v>7308005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633207</v>
+        <v>119633173</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763047</v>
+        <v>763074</v>
       </c>
       <c r="R17" t="n">
-        <v>7308005</v>
+        <v>7308093</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633201</v>
+        <v>119633155</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,25 +2859,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>763056</v>
+        <v>763047</v>
       </c>
       <c r="R22" t="n">
-        <v>7308031</v>
+        <v>7308003</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119633163</v>
+        <v>119633201</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,25 +2961,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762953</v>
+        <v>763056</v>
       </c>
       <c r="R23" t="n">
-        <v>7308131</v>
+        <v>7308031</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633155</v>
+        <v>119633163</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>763047</v>
+        <v>762953</v>
       </c>
       <c r="R24" t="n">
-        <v>7308003</v>
+        <v>7308131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633156</v>
+        <v>119633199</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3165,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>763021</v>
+        <v>763016</v>
       </c>
       <c r="R25" t="n">
-        <v>7308073</v>
+        <v>7308037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633199</v>
+        <v>119633170</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>93935</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2387</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763016</v>
+        <v>763074</v>
       </c>
       <c r="R26" t="n">
-        <v>7308037</v>
+        <v>7308155</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633170</v>
+        <v>119633156</v>
       </c>
       <c r="B27" t="n">
-        <v>93935</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,25 +3369,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2387</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763074</v>
+        <v>763021</v>
       </c>
       <c r="R27" t="n">
-        <v>7308155</v>
+        <v>7308073</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119633192</v>
+        <v>119633168</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>97941</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>762993</v>
+        <v>763065</v>
       </c>
       <c r="R43" t="n">
-        <v>7308094</v>
+        <v>7308164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633168</v>
+        <v>119633192</v>
       </c>
       <c r="B44" t="n">
-        <v>97941</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763065</v>
+        <v>762993</v>
       </c>
       <c r="R44" t="n">
-        <v>7308164</v>
+        <v>7308094</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119633140</v>
+        <v>119633202</v>
       </c>
       <c r="B9" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763083</v>
+        <v>763053</v>
       </c>
       <c r="R9" t="n">
-        <v>7308099</v>
+        <v>7307990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633189</v>
+        <v>119633176</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762957</v>
+        <v>763069</v>
       </c>
       <c r="R10" t="n">
-        <v>7308152</v>
+        <v>7308161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633162</v>
+        <v>119633161</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763091</v>
+        <v>763036</v>
       </c>
       <c r="R11" t="n">
-        <v>7308033</v>
+        <v>7308015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633179</v>
+        <v>119633167</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763037</v>
+        <v>763047</v>
       </c>
       <c r="R12" t="n">
-        <v>7308211</v>
+        <v>7308008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633205</v>
+        <v>119633162</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763062</v>
+        <v>763091</v>
       </c>
       <c r="R13" t="n">
-        <v>7308017</v>
+        <v>7308033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633190</v>
+        <v>119633178</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762983</v>
+        <v>763088</v>
       </c>
       <c r="R14" t="n">
-        <v>7308145</v>
+        <v>7308206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633182</v>
+        <v>119633172</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,25 +2145,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762980</v>
+        <v>763017</v>
       </c>
       <c r="R15" t="n">
-        <v>7308167</v>
+        <v>7308064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633207</v>
+        <v>119633159</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763047</v>
+        <v>763019</v>
       </c>
       <c r="R16" t="n">
-        <v>7308005</v>
+        <v>7308034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633173</v>
+        <v>119633189</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763074</v>
+        <v>762957</v>
       </c>
       <c r="R17" t="n">
-        <v>7308093</v>
+        <v>7308152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633195</v>
+        <v>119633199</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763021</v>
+        <v>763016</v>
       </c>
       <c r="R18" t="n">
-        <v>7308061</v>
+        <v>7308037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633197</v>
+        <v>119633196</v>
       </c>
       <c r="B19" t="n">
         <v>91840</v>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763052</v>
+        <v>763027</v>
       </c>
       <c r="R19" t="n">
-        <v>7308043</v>
+        <v>7308050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119633202</v>
+        <v>119633164</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>763053</v>
+        <v>762989</v>
       </c>
       <c r="R20" t="n">
-        <v>7307990</v>
+        <v>7308098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119633167</v>
+        <v>119633203</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>763047</v>
+        <v>762970</v>
       </c>
       <c r="R21" t="n">
-        <v>7308008</v>
+        <v>7308156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633155</v>
+        <v>119633148</v>
       </c>
       <c r="B22" t="n">
         <v>91884</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>763047</v>
+        <v>762994</v>
       </c>
       <c r="R22" t="n">
-        <v>7308003</v>
+        <v>7308094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119633201</v>
+        <v>119633174</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,25 +2961,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>763056</v>
+        <v>763074</v>
       </c>
       <c r="R23" t="n">
-        <v>7308031</v>
+        <v>7308105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633163</v>
+        <v>119633194</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,25 +3063,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762953</v>
+        <v>763027</v>
       </c>
       <c r="R24" t="n">
-        <v>7308131</v>
+        <v>7308069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633199</v>
+        <v>119633198</v>
       </c>
       <c r="B25" t="n">
         <v>91840</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>763016</v>
+        <v>763018</v>
       </c>
       <c r="R25" t="n">
-        <v>7308037</v>
+        <v>7308043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633170</v>
+        <v>119693821</v>
       </c>
       <c r="B26" t="n">
-        <v>93935</v>
+        <v>91310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2387</v>
+        <v>1958</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763074</v>
+        <v>762948</v>
       </c>
       <c r="R26" t="n">
-        <v>7308155</v>
+        <v>7308159</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633156</v>
+        <v>119633143</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,25 +3369,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763021</v>
+        <v>762995</v>
       </c>
       <c r="R27" t="n">
-        <v>7308073</v>
+        <v>7308094</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,6 +3433,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119633145</v>
+        <v>119633205</v>
       </c>
       <c r="B28" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,21 +3480,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3504,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>763013</v>
+        <v>763062</v>
       </c>
       <c r="R28" t="n">
-        <v>7308032</v>
+        <v>7308017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633206</v>
+        <v>119633155</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3604,7 +3609,7 @@
         <v>763047</v>
       </c>
       <c r="R29" t="n">
-        <v>7308006</v>
+        <v>7308003</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633198</v>
+        <v>119633145</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,25 +3680,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763018</v>
+        <v>763013</v>
       </c>
       <c r="R30" t="n">
-        <v>7308043</v>
+        <v>7308032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633183</v>
+        <v>119633142</v>
       </c>
       <c r="B31" t="n">
-        <v>89252</v>
+        <v>89275</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3781,21 +3786,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6276</v>
+        <v>6286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>763073</v>
+        <v>762980</v>
       </c>
       <c r="R31" t="n">
-        <v>7307993</v>
+        <v>7308130</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119633172</v>
+        <v>119633140</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3883,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>763017</v>
+        <v>763083</v>
       </c>
       <c r="R32" t="n">
-        <v>7308064</v>
+        <v>7308099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633169</v>
+        <v>119633207</v>
       </c>
       <c r="B33" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,21 +3990,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>762961</v>
+        <v>763047</v>
       </c>
       <c r="R33" t="n">
-        <v>7308137</v>
+        <v>7308005</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4076,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119633176</v>
+        <v>119633177</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4111,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>763069</v>
+        <v>763084</v>
       </c>
       <c r="R34" t="n">
-        <v>7308161</v>
+        <v>7308169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4178,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119633181</v>
+        <v>119633166</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,25 +4190,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762986</v>
+        <v>763003</v>
       </c>
       <c r="R35" t="n">
-        <v>7308167</v>
+        <v>7308087</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4280,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119633161</v>
+        <v>119633163</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,21 +4296,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>763036</v>
+        <v>762953</v>
       </c>
       <c r="R36" t="n">
-        <v>7308015</v>
+        <v>7308131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119633166</v>
+        <v>119633147</v>
       </c>
       <c r="B37" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,21 +4398,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>763003</v>
+        <v>762967</v>
       </c>
       <c r="R37" t="n">
-        <v>7308087</v>
+        <v>7308150</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119633141</v>
+        <v>119633181</v>
       </c>
       <c r="B38" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,25 +4496,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4519,10 +4524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762975</v>
+        <v>762986</v>
       </c>
       <c r="R38" t="n">
-        <v>7308144</v>
+        <v>7308167</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,10 +4586,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119633150</v>
+        <v>119633175</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4593,25 +4598,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4621,10 +4626,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>763017</v>
+        <v>763065</v>
       </c>
       <c r="R39" t="n">
-        <v>7308038</v>
+        <v>7308131</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,10 +4688,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119633174</v>
+        <v>119633156</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4695,25 +4700,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4723,10 +4728,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>763074</v>
+        <v>763021</v>
       </c>
       <c r="R40" t="n">
-        <v>7308105</v>
+        <v>7308073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,10 +4790,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119633149</v>
+        <v>119633197</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4797,25 +4802,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>763032</v>
+        <v>763052</v>
       </c>
       <c r="R41" t="n">
-        <v>7308054</v>
+        <v>7308043</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4887,10 +4892,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119633148</v>
+        <v>119633157</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>57326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4903,21 +4908,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4927,10 +4932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>762994</v>
+        <v>763063</v>
       </c>
       <c r="R42" t="n">
-        <v>7308094</v>
+        <v>7308218</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,10 +4994,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119633168</v>
+        <v>119633195</v>
       </c>
       <c r="B43" t="n">
-        <v>97941</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5005,21 +5010,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>763065</v>
+        <v>763021</v>
       </c>
       <c r="R43" t="n">
-        <v>7308164</v>
+        <v>7308061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,10 +5096,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633192</v>
+        <v>119633152</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5103,25 +5108,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5131,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>762993</v>
+        <v>763018</v>
       </c>
       <c r="R44" t="n">
-        <v>7308094</v>
+        <v>7308029</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633159</v>
+        <v>119633179</v>
       </c>
       <c r="B45" t="n">
-        <v>91856</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5205,25 +5210,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763019</v>
+        <v>763037</v>
       </c>
       <c r="R45" t="n">
-        <v>7308034</v>
+        <v>7308211</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,10 +5300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633204</v>
+        <v>119633169</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5311,21 +5316,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5335,10 +5340,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>763023</v>
+        <v>762961</v>
       </c>
       <c r="R46" t="n">
-        <v>7308047</v>
+        <v>7308137</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5397,10 +5402,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633143</v>
+        <v>119633204</v>
       </c>
       <c r="B47" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5409,25 +5414,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762995</v>
+        <v>763023</v>
       </c>
       <c r="R47" t="n">
-        <v>7308094</v>
+        <v>7308047</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5473,11 +5478,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5504,10 +5504,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119633157</v>
+        <v>119633206</v>
       </c>
       <c r="B48" t="n">
-        <v>57326</v>
+        <v>91834</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>763063</v>
+        <v>763047</v>
       </c>
       <c r="R48" t="n">
-        <v>7308218</v>
+        <v>7308006</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5606,10 +5606,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633164</v>
+        <v>119633153</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5622,21 +5622,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762989</v>
+        <v>763033</v>
       </c>
       <c r="R49" t="n">
-        <v>7308098</v>
+        <v>7308027</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5708,10 +5708,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633200</v>
+        <v>119633173</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5720,25 +5720,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>763027</v>
+        <v>763074</v>
       </c>
       <c r="R50" t="n">
-        <v>7308025</v>
+        <v>7308093</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119633191</v>
+        <v>119633200</v>
       </c>
       <c r="B51" t="n">
         <v>91840</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762980</v>
+        <v>763027</v>
       </c>
       <c r="R51" t="n">
-        <v>7308100</v>
+        <v>7308025</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119633142</v>
+        <v>119633141</v>
       </c>
       <c r="B52" t="n">
-        <v>89275</v>
+        <v>87406</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5924,25 +5924,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6286</v>
+        <v>4412</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762980</v>
+        <v>762975</v>
       </c>
       <c r="R52" t="n">
-        <v>7308130</v>
+        <v>7308144</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6014,10 +6014,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119633153</v>
+        <v>119633190</v>
       </c>
       <c r="B53" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6026,25 +6026,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>763033</v>
+        <v>762983</v>
       </c>
       <c r="R53" t="n">
-        <v>7308027</v>
+        <v>7308145</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119633152</v>
+        <v>119633191</v>
       </c>
       <c r="B54" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6128,25 +6128,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>763018</v>
+        <v>762980</v>
       </c>
       <c r="R54" t="n">
-        <v>7308029</v>
+        <v>7308100</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119693821</v>
+        <v>119633170</v>
       </c>
       <c r="B55" t="n">
-        <v>91310</v>
+        <v>93935</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1958</v>
+        <v>2387</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>762948</v>
+        <v>763074</v>
       </c>
       <c r="R55" t="n">
-        <v>7308159</v>
+        <v>7308155</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119633194</v>
+        <v>119633150</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6332,25 +6332,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>763027</v>
+        <v>763017</v>
       </c>
       <c r="R56" t="n">
-        <v>7308069</v>
+        <v>7308038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119633203</v>
+        <v>119633182</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6434,25 +6434,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762970</v>
+        <v>762980</v>
       </c>
       <c r="R57" t="n">
-        <v>7308156</v>
+        <v>7308167</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119633160</v>
+        <v>119633149</v>
       </c>
       <c r="B58" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763056</v>
+        <v>763032</v>
       </c>
       <c r="R58" t="n">
-        <v>7308022</v>
+        <v>7308054</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6626,7 +6626,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119633196</v>
+        <v>119633201</v>
       </c>
       <c r="B59" t="n">
         <v>91840</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>763027</v>
+        <v>763056</v>
       </c>
       <c r="R59" t="n">
-        <v>7308050</v>
+        <v>7308031</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633147</v>
+        <v>119633192</v>
       </c>
       <c r="B60" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6740,25 +6740,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762967</v>
+        <v>762993</v>
       </c>
       <c r="R60" t="n">
-        <v>7308150</v>
+        <v>7308094</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633177</v>
+        <v>119633183</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>89252</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6276</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>763084</v>
+        <v>763073</v>
       </c>
       <c r="R61" t="n">
-        <v>7308169</v>
+        <v>7307993</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119633178</v>
+        <v>119633168</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>97941</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6944,25 +6944,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>763088</v>
+        <v>763065</v>
       </c>
       <c r="R62" t="n">
-        <v>7308206</v>
+        <v>7308164</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119633175</v>
+        <v>119633160</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>91856</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>763065</v>
+        <v>763056</v>
       </c>
       <c r="R63" t="n">
-        <v>7308131</v>
+        <v>7308022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633167</v>
+        <v>119633172</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>78262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763047</v>
+        <v>763017</v>
       </c>
       <c r="R12" t="n">
-        <v>7308008</v>
+        <v>7308064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633162</v>
+        <v>119633159</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763091</v>
+        <v>763019</v>
       </c>
       <c r="R13" t="n">
-        <v>7308033</v>
+        <v>7308034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633178</v>
+        <v>119633167</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763088</v>
+        <v>763047</v>
       </c>
       <c r="R14" t="n">
-        <v>7308206</v>
+        <v>7308008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633172</v>
+        <v>119633162</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763017</v>
+        <v>763091</v>
       </c>
       <c r="R15" t="n">
-        <v>7308064</v>
+        <v>7308033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633159</v>
+        <v>119633189</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763019</v>
+        <v>762957</v>
       </c>
       <c r="R16" t="n">
-        <v>7308034</v>
+        <v>7308152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633189</v>
+        <v>119633199</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762957</v>
+        <v>763016</v>
       </c>
       <c r="R17" t="n">
-        <v>7308152</v>
+        <v>7308037</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633199</v>
+        <v>119633196</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763016</v>
+        <v>763027</v>
       </c>
       <c r="R18" t="n">
-        <v>7308037</v>
+        <v>7308050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633196</v>
+        <v>119633178</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763027</v>
+        <v>763088</v>
       </c>
       <c r="R19" t="n">
-        <v>7308050</v>
+        <v>7308206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119693821</v>
+        <v>119633205</v>
       </c>
       <c r="B26" t="n">
-        <v>91310</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>762948</v>
+        <v>763062</v>
       </c>
       <c r="R26" t="n">
-        <v>7308159</v>
+        <v>7308017</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633143</v>
+        <v>119633155</v>
       </c>
       <c r="B27" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,25 +3369,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762995</v>
+        <v>763047</v>
       </c>
       <c r="R27" t="n">
-        <v>7308094</v>
+        <v>7308003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,11 +3433,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119633205</v>
+        <v>119693821</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3476,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>763062</v>
+        <v>762948</v>
       </c>
       <c r="R28" t="n">
-        <v>7308017</v>
+        <v>7308159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633155</v>
+        <v>119633143</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,25 +3573,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>763047</v>
+        <v>762995</v>
       </c>
       <c r="R29" t="n">
-        <v>7308003</v>
+        <v>7308094</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,6 +3637,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5606,10 +5606,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633153</v>
+        <v>119633173</v>
       </c>
       <c r="B49" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5618,25 +5618,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>763033</v>
+        <v>763074</v>
       </c>
       <c r="R49" t="n">
-        <v>7308027</v>
+        <v>7308093</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5708,10 +5708,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633173</v>
+        <v>119633153</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5720,25 +5720,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>763074</v>
+        <v>763033</v>
       </c>
       <c r="R50" t="n">
-        <v>7308093</v>
+        <v>7308027</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119633149</v>
+        <v>119633183</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6536,25 +6536,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763032</v>
+        <v>763073</v>
       </c>
       <c r="R58" t="n">
-        <v>7308054</v>
+        <v>7307993</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119633201</v>
+        <v>119633149</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6638,25 +6638,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>763056</v>
+        <v>763032</v>
       </c>
       <c r="R59" t="n">
-        <v>7308031</v>
+        <v>7308054</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633192</v>
+        <v>119633201</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762993</v>
+        <v>763056</v>
       </c>
       <c r="R60" t="n">
-        <v>7308094</v>
+        <v>7308031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633183</v>
+        <v>119633192</v>
       </c>
       <c r="B61" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6842,25 +6842,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>763073</v>
+        <v>762993</v>
       </c>
       <c r="R61" t="n">
-        <v>7307993</v>
+        <v>7308094</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633172</v>
+        <v>119633167</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763017</v>
+        <v>763047</v>
       </c>
       <c r="R12" t="n">
-        <v>7308064</v>
+        <v>7308008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633159</v>
+        <v>119633162</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763019</v>
+        <v>763091</v>
       </c>
       <c r="R13" t="n">
-        <v>7308034</v>
+        <v>7308033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633167</v>
+        <v>119633178</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763047</v>
+        <v>763088</v>
       </c>
       <c r="R14" t="n">
-        <v>7308008</v>
+        <v>7308206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633162</v>
+        <v>119633172</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>78262</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763091</v>
+        <v>763017</v>
       </c>
       <c r="R15" t="n">
-        <v>7308033</v>
+        <v>7308064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633189</v>
+        <v>119633159</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762957</v>
+        <v>763019</v>
       </c>
       <c r="R16" t="n">
-        <v>7308152</v>
+        <v>7308034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633199</v>
+        <v>119633189</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763016</v>
+        <v>762957</v>
       </c>
       <c r="R17" t="n">
-        <v>7308037</v>
+        <v>7308152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633196</v>
+        <v>119633199</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763027</v>
+        <v>763016</v>
       </c>
       <c r="R18" t="n">
-        <v>7308050</v>
+        <v>7308037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633178</v>
+        <v>119633196</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763088</v>
+        <v>763027</v>
       </c>
       <c r="R19" t="n">
-        <v>7308206</v>
+        <v>7308050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -5606,10 +5606,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633173</v>
+        <v>119633153</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5618,25 +5618,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>763074</v>
+        <v>763033</v>
       </c>
       <c r="R49" t="n">
-        <v>7308093</v>
+        <v>7308027</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5708,10 +5708,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633153</v>
+        <v>119633173</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5720,25 +5720,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>763033</v>
+        <v>763074</v>
       </c>
       <c r="R50" t="n">
-        <v>7308027</v>
+        <v>7308093</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119633170</v>
+        <v>119633150</v>
       </c>
       <c r="B55" t="n">
-        <v>93935</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2387</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>763074</v>
+        <v>763017</v>
       </c>
       <c r="R55" t="n">
-        <v>7308155</v>
+        <v>7308038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119633150</v>
+        <v>119633170</v>
       </c>
       <c r="B56" t="n">
-        <v>91884</v>
+        <v>93935</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6332,25 +6332,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>2387</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>763017</v>
+        <v>763074</v>
       </c>
       <c r="R56" t="n">
-        <v>7308038</v>
+        <v>7308155</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633167</v>
+        <v>119633172</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>78262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763047</v>
+        <v>763017</v>
       </c>
       <c r="R12" t="n">
-        <v>7308008</v>
+        <v>7308064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633162</v>
+        <v>119633159</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763091</v>
+        <v>763019</v>
       </c>
       <c r="R13" t="n">
-        <v>7308033</v>
+        <v>7308034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633178</v>
+        <v>119633167</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763088</v>
+        <v>763047</v>
       </c>
       <c r="R14" t="n">
-        <v>7308206</v>
+        <v>7308008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633172</v>
+        <v>119633162</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763017</v>
+        <v>763091</v>
       </c>
       <c r="R15" t="n">
-        <v>7308064</v>
+        <v>7308033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633159</v>
+        <v>119633189</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763019</v>
+        <v>762957</v>
       </c>
       <c r="R16" t="n">
-        <v>7308034</v>
+        <v>7308152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633189</v>
+        <v>119633199</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762957</v>
+        <v>763016</v>
       </c>
       <c r="R17" t="n">
-        <v>7308152</v>
+        <v>7308037</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633199</v>
+        <v>119633196</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763016</v>
+        <v>763027</v>
       </c>
       <c r="R18" t="n">
-        <v>7308037</v>
+        <v>7308050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633196</v>
+        <v>119633178</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763027</v>
+        <v>763088</v>
       </c>
       <c r="R19" t="n">
-        <v>7308050</v>
+        <v>7308206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633152</v>
+        <v>119633204</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5112,21 +5112,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763018</v>
+        <v>763023</v>
       </c>
       <c r="R44" t="n">
-        <v>7308029</v>
+        <v>7308047</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633179</v>
+        <v>119633152</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5210,25 +5210,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763037</v>
+        <v>763018</v>
       </c>
       <c r="R45" t="n">
-        <v>7308211</v>
+        <v>7308029</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633169</v>
+        <v>119633179</v>
       </c>
       <c r="B46" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5312,25 +5312,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762961</v>
+        <v>763037</v>
       </c>
       <c r="R46" t="n">
-        <v>7308137</v>
+        <v>7308211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633204</v>
+        <v>119633169</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5418,21 +5418,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>763023</v>
+        <v>762961</v>
       </c>
       <c r="R47" t="n">
-        <v>7308047</v>
+        <v>7308137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119633202</v>
+        <v>119633161</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763053</v>
+        <v>763036</v>
       </c>
       <c r="R9" t="n">
-        <v>7307990</v>
+        <v>7308015</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633176</v>
+        <v>119633202</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763069</v>
+        <v>763053</v>
       </c>
       <c r="R10" t="n">
-        <v>7308161</v>
+        <v>7307990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633161</v>
+        <v>119633176</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,25 +1737,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763036</v>
+        <v>763069</v>
       </c>
       <c r="R11" t="n">
-        <v>7308015</v>
+        <v>7308161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633172</v>
+        <v>119633167</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763017</v>
+        <v>763047</v>
       </c>
       <c r="R12" t="n">
-        <v>7308064</v>
+        <v>7308008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633159</v>
+        <v>119633162</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763019</v>
+        <v>763091</v>
       </c>
       <c r="R13" t="n">
-        <v>7308034</v>
+        <v>7308033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633167</v>
+        <v>119633178</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763047</v>
+        <v>763088</v>
       </c>
       <c r="R14" t="n">
-        <v>7308008</v>
+        <v>7308206</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633162</v>
+        <v>119633172</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>78262</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763091</v>
+        <v>763017</v>
       </c>
       <c r="R15" t="n">
-        <v>7308033</v>
+        <v>7308064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633189</v>
+        <v>119633159</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762957</v>
+        <v>763019</v>
       </c>
       <c r="R16" t="n">
-        <v>7308152</v>
+        <v>7308034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633199</v>
+        <v>119633189</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763016</v>
+        <v>762957</v>
       </c>
       <c r="R17" t="n">
-        <v>7308037</v>
+        <v>7308152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633196</v>
+        <v>119633199</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763027</v>
+        <v>763016</v>
       </c>
       <c r="R18" t="n">
-        <v>7308050</v>
+        <v>7308037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633178</v>
+        <v>119633196</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763088</v>
+        <v>763027</v>
       </c>
       <c r="R19" t="n">
-        <v>7308206</v>
+        <v>7308050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633204</v>
+        <v>119633152</v>
       </c>
       <c r="B44" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5112,21 +5112,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763023</v>
+        <v>763018</v>
       </c>
       <c r="R44" t="n">
-        <v>7308047</v>
+        <v>7308029</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633152</v>
+        <v>119633179</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5210,25 +5210,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763018</v>
+        <v>763037</v>
       </c>
       <c r="R45" t="n">
-        <v>7308029</v>
+        <v>7308211</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633179</v>
+        <v>119633169</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5312,25 +5312,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>763037</v>
+        <v>762961</v>
       </c>
       <c r="R46" t="n">
-        <v>7308211</v>
+        <v>7308137</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633169</v>
+        <v>119633204</v>
       </c>
       <c r="B47" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5418,21 +5418,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762961</v>
+        <v>763023</v>
       </c>
       <c r="R47" t="n">
-        <v>7308137</v>
+        <v>7308047</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -3255,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119633205</v>
+        <v>119693821</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>91310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,25 +3267,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763062</v>
+        <v>762948</v>
       </c>
       <c r="R26" t="n">
-        <v>7308017</v>
+        <v>7308159</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633155</v>
+        <v>119633143</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,25 +3369,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>763047</v>
+        <v>762995</v>
       </c>
       <c r="R27" t="n">
-        <v>7308003</v>
+        <v>7308094</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,6 +3433,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119693821</v>
+        <v>119633205</v>
       </c>
       <c r="B28" t="n">
-        <v>91310</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3476,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3504,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>762948</v>
+        <v>763062</v>
       </c>
       <c r="R28" t="n">
-        <v>7308159</v>
+        <v>7308017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3561,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633143</v>
+        <v>119633155</v>
       </c>
       <c r="B29" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3573,25 +3578,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762995</v>
+        <v>763047</v>
       </c>
       <c r="R29" t="n">
-        <v>7308094</v>
+        <v>7308003</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,11 +3642,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -3977,7 +3977,7 @@
         <v>119633207</v>
       </c>
       <c r="B33" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79486205</v>
+        <v>117664473</v>
       </c>
       <c r="B2" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763023.0399413325</v>
+        <v>762931</v>
       </c>
       <c r="R2" t="n">
-        <v>7308062.390208935</v>
+        <v>7308402</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,75 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79504893</v>
+        <v>119693821</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763023.0399413325</v>
+        <v>762948</v>
       </c>
       <c r="R3" t="n">
-        <v>7308062.390208935</v>
+        <v>7308159</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,100 +851,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79504839</v>
+        <v>119633159</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763023.0399413325</v>
+        <v>763019</v>
       </c>
       <c r="R4" t="n">
-        <v>7308062.390208935</v>
+        <v>7308034</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,101 +948,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79384381</v>
+        <v>119633160</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763046.2548724541</v>
+        <v>763056</v>
       </c>
       <c r="R5" t="n">
-        <v>7308308.861253065</v>
+        <v>7308022</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,76 +1045,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117664460</v>
+        <v>119633161</v>
       </c>
       <c r="B6" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762971</v>
+        <v>763036</v>
       </c>
       <c r="R6" t="n">
-        <v>7308322</v>
+        <v>7308015</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,67 +1153,55 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117660016</v>
+        <v>119633170</v>
       </c>
       <c r="B7" t="n">
-        <v>78219</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763017</v>
+        <v>763074</v>
       </c>
       <c r="R7" t="n">
-        <v>7308299</v>
+        <v>7308155</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117659625</v>
+        <v>119633145</v>
       </c>
       <c r="B8" t="n">
-        <v>78218</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,44 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällberg väg, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763017</v>
+        <v>763013</v>
       </c>
       <c r="R8" t="n">
-        <v>7308302</v>
+        <v>7308032</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1336,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1521,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119633161</v>
+        <v>119633162</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763036</v>
+        <v>763091</v>
       </c>
       <c r="R9" t="n">
-        <v>7308015</v>
+        <v>7308033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119633202</v>
+        <v>119633163</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763053</v>
+        <v>762953</v>
       </c>
       <c r="R10" t="n">
-        <v>7307990</v>
+        <v>7308131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633176</v>
+        <v>119633164</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763069</v>
+        <v>762989</v>
       </c>
       <c r="R11" t="n">
-        <v>7308161</v>
+        <v>7308098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119633167</v>
+        <v>119633166</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763047</v>
+        <v>763003</v>
       </c>
       <c r="R12" t="n">
-        <v>7308008</v>
+        <v>7308087</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633162</v>
+        <v>119633167</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763091</v>
+        <v>763047</v>
       </c>
       <c r="R13" t="n">
-        <v>7308033</v>
+        <v>7308008</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119633178</v>
+        <v>119633203</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763088</v>
+        <v>762970</v>
       </c>
       <c r="R14" t="n">
-        <v>7308206</v>
+        <v>7308156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633172</v>
+        <v>119633204</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763017</v>
+        <v>763023</v>
       </c>
       <c r="R15" t="n">
-        <v>7308064</v>
+        <v>7308047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119633159</v>
+        <v>119633205</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763019</v>
+        <v>763062</v>
       </c>
       <c r="R16" t="n">
-        <v>7308034</v>
+        <v>7308017</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119633189</v>
+        <v>119633206</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762957</v>
+        <v>763047</v>
       </c>
       <c r="R17" t="n">
-        <v>7308152</v>
+        <v>7308006</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119633199</v>
+        <v>119633207</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763016</v>
+        <v>763047</v>
       </c>
       <c r="R18" t="n">
-        <v>7308037</v>
+        <v>7308005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,19 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119633196</v>
+        <v>119633189</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2581,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763027</v>
+        <v>762957</v>
       </c>
       <c r="R19" t="n">
-        <v>7308050</v>
+        <v>7308152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2643,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119633164</v>
+        <v>119633190</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2659,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2683,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762989</v>
+        <v>762983</v>
       </c>
       <c r="R20" t="n">
-        <v>7308098</v>
+        <v>7308145</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119633203</v>
+        <v>119633191</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2761,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762970</v>
+        <v>762980</v>
       </c>
       <c r="R21" t="n">
-        <v>7308156</v>
+        <v>7308100</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633148</v>
+        <v>119633192</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2863,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,7 +2650,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762994</v>
+        <v>762993</v>
       </c>
       <c r="R22" t="n">
         <v>7308094</v>
@@ -2949,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119633174</v>
+        <v>119633194</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>763074</v>
+        <v>763027</v>
       </c>
       <c r="R23" t="n">
-        <v>7308105</v>
+        <v>7308069</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,19 +2809,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119633194</v>
+        <v>119633195</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3091,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>763027</v>
+        <v>763021</v>
       </c>
       <c r="R24" t="n">
-        <v>7308069</v>
+        <v>7308061</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,19 +2906,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119633198</v>
+        <v>119633196</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3193,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>763018</v>
+        <v>763027</v>
       </c>
       <c r="R25" t="n">
-        <v>7308043</v>
+        <v>7308050</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119693821</v>
+        <v>119633197</v>
       </c>
       <c r="B26" t="n">
-        <v>91310</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>762948</v>
+        <v>763052</v>
       </c>
       <c r="R26" t="n">
-        <v>7308159</v>
+        <v>7308043</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119633143</v>
+        <v>119633198</v>
       </c>
       <c r="B27" t="n">
-        <v>89275</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762995</v>
+        <v>763018</v>
       </c>
       <c r="R27" t="n">
-        <v>7308094</v>
+        <v>7308043</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,11 +3171,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119633205</v>
+        <v>119633199</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>763062</v>
+        <v>763016</v>
       </c>
       <c r="R28" t="n">
-        <v>7308017</v>
+        <v>7308037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119633155</v>
+        <v>119633200</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>763047</v>
+        <v>763027</v>
       </c>
       <c r="R29" t="n">
-        <v>7308003</v>
+        <v>7308025</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3668,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119633145</v>
+        <v>119633201</v>
       </c>
       <c r="B30" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>763013</v>
+        <v>763056</v>
       </c>
       <c r="R30" t="n">
-        <v>7308032</v>
+        <v>7308031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3770,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119633142</v>
+        <v>119633202</v>
       </c>
       <c r="B31" t="n">
-        <v>89275</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3810,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>762980</v>
+        <v>763053</v>
       </c>
       <c r="R31" t="n">
-        <v>7308130</v>
+        <v>7307990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,12 +3588,7 @@
         <v>119633140</v>
       </c>
       <c r="B32" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3974,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119633207</v>
+        <v>119633141</v>
       </c>
       <c r="B33" t="n">
-        <v>91967</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4014,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763047</v>
+        <v>762975</v>
       </c>
       <c r="R33" t="n">
-        <v>7308005</v>
+        <v>7308144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,37 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119633177</v>
+        <v>119633147</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4116,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>763084</v>
+        <v>762967</v>
       </c>
       <c r="R34" t="n">
-        <v>7308169</v>
+        <v>7308150</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,37 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119633166</v>
+        <v>119633183</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4218,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>763003</v>
+        <v>763073</v>
       </c>
       <c r="R35" t="n">
-        <v>7308087</v>
+        <v>7307993</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4280,37 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119633163</v>
+        <v>119633142</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4320,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>762953</v>
+        <v>762980</v>
       </c>
       <c r="R36" t="n">
-        <v>7308131</v>
+        <v>7308130</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4382,37 +4070,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119633147</v>
+        <v>119633143</v>
       </c>
       <c r="B37" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>6286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4422,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>762967</v>
+        <v>762995</v>
       </c>
       <c r="R37" t="n">
-        <v>7308150</v>
+        <v>7308094</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,6 +4141,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>spermatiskdoft</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4484,53 +4172,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119633181</v>
+        <v>79504839</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762986</v>
+        <v>763023</v>
       </c>
       <c r="R38" t="n">
-        <v>7308167</v>
+        <v>7308062</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4554,12 +4240,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4568,71 +4254,99 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119633175</v>
+        <v>117659625</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>763065</v>
+        <v>763017</v>
       </c>
       <c r="R39" t="n">
-        <v>7308131</v>
+        <v>7308302</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4656,12 +4370,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4670,6 +4384,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4688,15 +4403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119633156</v>
+        <v>119633172</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,21 +4414,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4728,10 +4438,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>763021</v>
+        <v>763017</v>
       </c>
       <c r="R40" t="n">
-        <v>7308073</v>
+        <v>7308064</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,15 +4500,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119633197</v>
+        <v>79486205</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,37 +4511,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>763052</v>
+        <v>763023</v>
       </c>
       <c r="R41" t="n">
-        <v>7308043</v>
+        <v>7308062</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4860,12 +4568,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4874,71 +4582,67 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119633157</v>
+        <v>117664465</v>
       </c>
       <c r="B42" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>763063</v>
+        <v>762925</v>
       </c>
       <c r="R42" t="n">
-        <v>7308218</v>
+        <v>7308403</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4962,12 +4666,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4994,15 +4698,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119633195</v>
+        <v>117664467</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5010,37 +4709,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>763021</v>
+        <v>762934</v>
       </c>
       <c r="R43" t="n">
-        <v>7308061</v>
+        <v>7308414</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5064,12 +4763,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5096,53 +4795,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119633152</v>
+        <v>117667686</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>763018</v>
+        <v>762976</v>
       </c>
       <c r="R44" t="n">
-        <v>7308029</v>
+        <v>7308367</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5166,12 +4868,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,49 +4893,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119633179</v>
+        <v>119633157</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5238,10 +4940,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>763037</v>
+        <v>763063</v>
       </c>
       <c r="R45" t="n">
-        <v>7308211</v>
+        <v>7308218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,53 +5002,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119633169</v>
+        <v>79384552</v>
       </c>
       <c r="B46" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762961</v>
+        <v>763066</v>
       </c>
       <c r="R46" t="n">
-        <v>7308137</v>
+        <v>7308364</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5370,12 +5076,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,65 +5096,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119633204</v>
+        <v>79384550</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>219874</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>763023</v>
+        <v>763066</v>
       </c>
       <c r="R47" t="n">
-        <v>7308047</v>
+        <v>7308364</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5472,12 +5182,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>21 överblommade ex. och 12 ex. med endast blad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5492,49 +5207,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119633206</v>
+        <v>119633168</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>219874</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5544,10 +5254,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>763047</v>
+        <v>763065</v>
       </c>
       <c r="R48" t="n">
-        <v>7308006</v>
+        <v>7308164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5606,53 +5316,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119633153</v>
+        <v>79384551</v>
       </c>
       <c r="B49" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>763033</v>
+        <v>763066</v>
       </c>
       <c r="R49" t="n">
-        <v>7308027</v>
+        <v>7308364</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5676,12 +5390,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5696,27 +5410,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119633173</v>
+        <v>117646699</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5741,20 +5450,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>763074</v>
+        <v>762936</v>
       </c>
       <c r="R50" t="n">
-        <v>7308093</v>
+        <v>7308406</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5778,12 +5499,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5792,55 +5513,51 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119633200</v>
+        <v>119633173</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5850,10 +5567,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>763027</v>
+        <v>763074</v>
       </c>
       <c r="R51" t="n">
-        <v>7308025</v>
+        <v>7308093</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5912,37 +5629,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119633141</v>
+        <v>119633174</v>
       </c>
       <c r="B52" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5952,10 +5664,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762975</v>
+        <v>763074</v>
       </c>
       <c r="R52" t="n">
-        <v>7308144</v>
+        <v>7308105</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6014,37 +5726,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119633190</v>
+        <v>119633175</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6054,10 +5761,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>762983</v>
+        <v>763065</v>
       </c>
       <c r="R53" t="n">
-        <v>7308145</v>
+        <v>7308131</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6116,37 +5823,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119633191</v>
+        <v>119633176</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6156,10 +5858,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>762980</v>
+        <v>763069</v>
       </c>
       <c r="R54" t="n">
-        <v>7308100</v>
+        <v>7308161</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6218,37 +5920,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119633150</v>
+        <v>119633177</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6258,10 +5955,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>763017</v>
+        <v>763084</v>
       </c>
       <c r="R55" t="n">
-        <v>7308038</v>
+        <v>7308169</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6320,37 +6017,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119633170</v>
+        <v>119633178</v>
       </c>
       <c r="B56" t="n">
-        <v>93935</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6360,10 +6052,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>763074</v>
+        <v>763088</v>
       </c>
       <c r="R56" t="n">
-        <v>7308155</v>
+        <v>7308206</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6422,15 +6114,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119633182</v>
+        <v>119633179</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6462,10 +6149,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762980</v>
+        <v>763037</v>
       </c>
       <c r="R57" t="n">
-        <v>7308167</v>
+        <v>7308211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6524,15 +6211,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119633183</v>
+        <v>119633181</v>
       </c>
       <c r="B58" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6540,21 +6222,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6276</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6564,10 +6246,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>763073</v>
+        <v>762986</v>
       </c>
       <c r="R58" t="n">
-        <v>7307993</v>
+        <v>7308167</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6626,37 +6308,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119633149</v>
+        <v>119633182</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6666,10 +6343,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>763032</v>
+        <v>762980</v>
       </c>
       <c r="R59" t="n">
-        <v>7308054</v>
+        <v>7308167</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6728,15 +6405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119633201</v>
+        <v>79384381</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6744,37 +6416,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>763056</v>
+        <v>763046</v>
       </c>
       <c r="R60" t="n">
-        <v>7308031</v>
+        <v>7308309</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6798,12 +6474,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6812,33 +6488,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119633192</v>
+        <v>79384415</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6846,37 +6518,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>762993</v>
+        <v>763092</v>
       </c>
       <c r="R61" t="n">
-        <v>7308094</v>
+        <v>7308366</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6900,12 +6576,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6914,33 +6590,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119633168</v>
+        <v>79384609</v>
       </c>
       <c r="B62" t="n">
-        <v>97941</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6948,37 +6620,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>763065</v>
+        <v>763090</v>
       </c>
       <c r="R62" t="n">
-        <v>7308164</v>
+        <v>7308363</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7002,12 +6678,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7016,71 +6692,67 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119633160</v>
+        <v>117664471</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>223591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fällberg väg, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>763056</v>
+        <v>762933</v>
       </c>
       <c r="R63" t="n">
-        <v>7308022</v>
+        <v>7308409</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7104,12 +6776,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7118,6 +6790,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7133,6 +6806,439 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>117660016</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>763017</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7308299</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>117660195</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>762948</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7308363</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>119633169</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fällberg väg, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>762961</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7308137</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>79504893</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>763023</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7308062</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2019-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2019-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Gårdman, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3573-2024 artfynd.xlsx
+++ b/artfynd/A 3573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119693821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633160</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633170</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633162</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633163</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633164</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633166</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633167</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633203</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633204</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633205</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633206</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633207</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633189</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633190</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633191</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633192</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633194</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633195</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633196</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633197</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633198</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633199</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633200</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633201</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633202</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633140</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633141</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633147</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633183</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633142</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633143</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79504839</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4400,6 +4590,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117659625</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4497,6 +4692,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633172</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4598,6 +4798,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79486205</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4695,6 +4900,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664465</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4792,6 +5002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664467</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4902,6 +5117,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117667686</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4999,6 +5219,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633157</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5105,6 +5330,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384552</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5216,6 +5446,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384550</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5313,6 +5548,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633168</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5419,6 +5659,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384551</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5529,6 +5774,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646699</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5626,6 +5876,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633173</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5723,6 +5978,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633174</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5820,6 +6080,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633175</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5917,6 +6182,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633176</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6014,6 +6284,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633177</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6111,6 +6386,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633178</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6208,6 +6488,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633179</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6305,6 +6590,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633181</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6402,6 +6692,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633182</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6504,6 +6799,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384381</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6606,6 +6906,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384415</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6708,6 +7013,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384609</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6806,6 +7116,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664471</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6911,6 +7226,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660016</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7016,6 +7336,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660195</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7113,6 +7438,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119633169</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7239,8 +7569,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79504893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>